--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1904,16 +1904,16 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1904,16 +1904,16 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL12"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,27 +633,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>45882.38541666666</v>
+        <v>45882.25</v>
       </c>
     </row>
     <row r="3">
@@ -765,7 +765,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>45882.41666666666</v>
+        <v>45882.38541666666</v>
       </c>
     </row>
     <row r="4">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>45882.45833333334</v>
+        <v>45882.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45882.5</v>
+        <v>45882.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>45882.5</v>
       </c>
     </row>
     <row r="8">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45882.79166666666</v>
+        <v>45882.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45882.79166666666</v>
+        <v>45882.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1953,129 +1953,1053 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kaizer Chiefs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Polokwane City</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL12" s="3" t="n">
+        <v>45882.60416666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Magesi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL13" s="3" t="n">
+        <v>45882.60416666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Golden Arrows</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Richards Bay</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL14" s="3" t="n">
+        <v>45882.60416666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Durban City</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Chippa United</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL15" s="3" t="n">
+        <v>45882.60416666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sekhukhune United</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TS Galaxy</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL16" s="3" t="n">
+        <v>45882.60416666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>45882.79166666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL18" s="3" t="n">
+        <v>45882.79166666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>South America Copa Libertadores</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="L19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC19" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL19" s="3" t="n">
         <v>45882.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AL18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.59</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>15.5</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.36</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="S12" t="n">
-        <v>2.85</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.6</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45882.60416666666</v>
+        <v>45882.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,40 +2654,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2714,10 +2714,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,40 +2786,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>3.66</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2828,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -2868,138 +2868,6 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45882.79166666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45882</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
         <v>45882.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>45882.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,34 +1862,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.92</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>5.75</v>
+        <v>3.53</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
         <v>2.02</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
         <v>9</v>
@@ -1901,37 +1901,37 @@
         <v>1.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.35</v>
+        <v>4.71</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AA11" t="n">
         <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="AE11" t="n">
         <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AH11" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="P12" t="n">
         <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.64</v>
       </c>
       <c r="S12" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
         <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
         <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,73 +2258,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.28</v>
+        <v>4.92</v>
       </c>
       <c r="M14" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.04</v>
+        <v>5.75</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="S14" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.3</v>
+        <v>4.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI14" t="n">
         <v>1.01</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>3.53</v>
@@ -1904,10 +1904,10 @@
         <v>4.71</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
         <v>3.2</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
         <v>3.04</v>
@@ -2036,10 +2036,10 @@
         <v>5.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
         <v>3.1</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,31 +2126,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>5.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="S13" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.2</v>
@@ -2162,40 +2162,40 @@
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.95</v>
+        <v>4.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="AE13" t="n">
         <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.92</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.55</v>
       </c>
-      <c r="N14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5.75</v>
-      </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.95</v>
+        <v>5.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
         <v>1.2</v>
@@ -2294,40 +2294,40 @@
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.35</v>
+        <v>4.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="AE14" t="n">
         <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AH14" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.95</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2564,16 +2564,16 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,40 +2654,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2714,10 +2714,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,34 +1862,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.53</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S11" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
         <v>9</v>
@@ -1898,34 +1898,34 @@
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.71</v>
+        <v>4.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AE11" t="n">
         <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AH11" t="n">
         <v>11</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,34 +2258,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
         <v>9</v>
@@ -2294,34 +2294,34 @@
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.95</v>
+        <v>4.71</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AE14" t="n">
         <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
         <v>11</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -674,40 +674,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="O2" t="n">
-        <v>2.92</v>
+        <v>1.8</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>17.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="T2" t="n">
         <v>2.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V2" t="n">
         <v>4.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -722,22 +722,22 @@
         <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
         <v>2.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AH2" t="n">
         <v>3.5</v>
@@ -1871,13 +1871,13 @@
         <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>5.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
         <v>1.64</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.04</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.3</v>
+        <v>4.71</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
         <v>6.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH12" t="n">
         <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2135,13 +2135,13 @@
         <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>5.75</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
         <v>1.68</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3.53</v>
+        <v>1.93</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.71</v>
+        <v>5.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
         <v>6.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
         <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2531,13 +2531,13 @@
         <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
         <v>1.53</v>
@@ -2795,13 +2795,13 @@
         <v>6.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL18"/>
+  <dimension ref="A1:AL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45882.45833333334</v>
+        <v>45882.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45882.5</v>
+        <v>45882.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>45882.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V9" t="n">
         <v>9</v>
       </c>
-      <c r="M9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>3.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>45882.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45882.58333333334</v>
+        <v>45882.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,34 +1994,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
         <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
         <v>2.02</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
         <v>9</v>
@@ -2033,37 +2033,37 @@
         <v>1.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.71</v>
+        <v>4.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AE12" t="n">
         <v>1.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,46 +2126,46 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>1.93</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="S13" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.35</v>
+        <v>5.3</v>
       </c>
       <c r="Z13" t="n">
         <v>1.5</v>
@@ -2174,25 +2174,25 @@
         <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AI13" t="n">
         <v>1.01</v>
@@ -2217,27 +2217,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45882.60416666666</v>
+        <v>45882.79166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2349,27 +2349,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45882.60416666666</v>
+        <v>45882.79166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,71 +2522,71 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.49</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.66</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.53</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V16" t="n">
-        <v>11</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
@@ -2604,270 +2604,6 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45882.79166666666</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45882</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blooming</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
-        <v>45882.79166666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45882</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
         <v>45882.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL16"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.8</v>
@@ -695,19 +695,19 @@
         <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
         <v>4.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -722,25 +722,25 @@
         <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AE2" t="n">
         <v>1.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG2" t="n">
         <v>2.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AI2" t="n">
         <v>1.22</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>45882.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>45882.5</v>
       </c>
     </row>
     <row r="8">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45882.58333333334</v>
+        <v>45882.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45882.60416666666</v>
+        <v>45882.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45882.60416666666</v>
+        <v>45882.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
         <v>2.95</v>
@@ -2012,19 +2012,19 @@
         <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U12" t="n">
         <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
@@ -2033,28 +2033,28 @@
         <v>1.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AE12" t="n">
         <v>1.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
         <v>1.45</v>
@@ -2063,7 +2063,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.93</v>
@@ -2144,7 +2144,7 @@
         <v>2.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
         <v>2.17</v>
@@ -2153,7 +2153,7 @@
         <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
         <v>9.9</v>
@@ -2165,37 +2165,37 @@
         <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
         <v>2.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AH13" t="n">
         <v>11</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2217,27 +2217,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.49</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>45882.79166666666</v>
+        <v>45882.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2349,27 +2349,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB15" t="n">
         <v>3.25</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>45882.79166666666</v>
+        <v>45882.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2481,129 +2481,525 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Durban City</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Chippa United</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL16" s="3" t="n">
+        <v>45882.60416666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>45882.79166666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL18" s="3" t="n">
+        <v>45882.79166666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>South America Copa Libertadores</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L19" t="n">
         <v>1.44</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M19" t="n">
         <v>3.66</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N19" t="n">
         <v>6.6</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O19" t="n">
         <v>1.44</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3.4</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R19" t="n">
         <v>1.44</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S19" t="n">
         <v>2.63</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T19" t="n">
         <v>3.25</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U19" t="n">
         <v>1.33</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V19" t="n">
         <v>10</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W19" t="n">
         <v>1.06</v>
       </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC19" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
         <v>2.38</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG19" t="n">
         <v>1.53</v>
       </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL19" s="3" t="n">
         <v>45882.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AL18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="O2" t="n">
         <v>1.8</v>
@@ -722,10 +722,10 @@
         <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
         <v>2.26</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>2.05</v>
@@ -1904,16 +1904,16 @@
         <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AD11" t="n">
         <v>6.5</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
         <v>2.95</v>
@@ -2036,13 +2036,13 @@
         <v>4.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AC12" t="n">
         <v>1.33</v>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.93</v>
@@ -2168,16 +2168,16 @@
         <v>5.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AD13" t="n">
         <v>6.1</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2.99</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.14</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45882.60416666666</v>
+        <v>45882.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,40 +2786,40 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="N18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.25</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -2868,138 +2868,6 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45882.79166666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45882</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>10</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
         <v>45882.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>45882.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,46 +1994,46 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>1.93</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="R12" t="n">
         <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
         <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
         <v>1.5</v>
@@ -2042,25 +2042,25 @@
         <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AH12" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>1.03</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S13" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V13" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AH13" t="n">
         <v>11</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.65</v>
@@ -2288,46 +2288,46 @@
         <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="Z14" t="n">
         <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
         <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AE13" t="n">
         <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
         <v>1.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
         <v>1.65</v>
@@ -2288,46 +2288,46 @@
         <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z14" t="n">
         <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.25</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="R15" t="n">
         <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="Z15" t="n">
         <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2564,16 +2564,16 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,40 +2654,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2714,10 +2714,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S15" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V15" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,40 +2522,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.53</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2564,16 +2564,16 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q18" t="n">
         <v>3.4</v>
@@ -2822,16 +2822,16 @@
         <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB18" t="n">
         <v>2.3</v>
@@ -2840,10 +2840,10 @@
         <v>1.63</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF18" t="n">
         <v>2.38</v>
@@ -2852,10 +2852,10 @@
         <v>1.53</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL18"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>3.63</v>
       </c>
       <c r="N2" t="n">
-        <v>2.06</v>
+        <v>2.59</v>
       </c>
       <c r="O2" t="n">
         <v>1.8</v>
@@ -692,22 +692,22 @@
         <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
         <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -728,22 +728,22 @@
         <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1070,22 +1070,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45882.58333333334</v>
+        <v>45882.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45882.79166666666</v>
+        <v>45882.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2745,129 +2745,261 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL18" s="3" t="n">
+        <v>45882.79166666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>South America Copa Libertadores</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Flamengo</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>1.44</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>3.66</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>6.6</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>1.44</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>8</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>3.4</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1.44</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>2.63</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>3.25</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1.33</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>10</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>1.06</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y19" t="n">
         <v>8</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z19" t="n">
         <v>1.42</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA19" t="n">
         <v>2.8</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB19" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC19" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD19" t="n">
         <v>4.33</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE19" t="n">
         <v>1.2</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AF19" t="n">
         <v>2.38</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG19" t="n">
         <v>1.53</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AH19" t="n">
         <v>8.5</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AI19" t="n">
         <v>1.06</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL19" s="3" t="n">
         <v>45882.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
         <v>1.8</v>
@@ -938,40 +938,40 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -980,34 +980,34 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,52 +1070,52 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
         <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB5" t="n">
         <v>1.55</v>
@@ -1124,22 +1124,22 @@
         <v>2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1220,58 +1220,58 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1337,73 +1337,73 @@
         <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.46</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>3.75</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.17</v>
       </c>
-      <c r="V11" t="n">
-        <v>9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>4.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.15</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.31</v>
+        <v>2.37</v>
       </c>
       <c r="AD11" t="n">
-        <v>6.5</v>
+        <v>2.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>1.56</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.42</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,70 +1994,70 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>4.71</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AD12" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AH12" t="n">
         <v>11</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,76 +2126,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>2.28</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>1.93</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="R13" t="n">
         <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="U13" t="n">
         <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.4</v>
+        <v>5.07</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH13" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="U14" t="n">
         <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF14" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="n">
         <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.95</v>
+        <v>2.07</v>
       </c>
       <c r="T16" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>3.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>6.25</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.39</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH16" t="n">
-        <v>5.14</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.8</v>
@@ -695,16 +695,16 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T2" t="n">
         <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="W2" t="n">
         <v>1.13</v>
@@ -722,16 +722,16 @@
         <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF2" t="n">
         <v>1.4</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,34 +938,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>4.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
         <v>4.5</v>
@@ -974,16 +974,16 @@
         <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AB4" t="n">
         <v>1.55</v>
@@ -998,16 +998,16 @@
         <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,34 +1070,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4.35</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
         <v>4.5</v>
@@ -1106,16 +1106,16 @@
         <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AB5" t="n">
         <v>1.55</v>
@@ -1130,16 +1130,16 @@
         <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1211,13 +1211,13 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
-        <v>1.89</v>
+        <v>1.23</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>45882.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.44</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH11" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1997,73 +1997,73 @@
         <v>2.35</v>
       </c>
       <c r="M12" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="S12" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
         <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.71</v>
+        <v>5.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD12" t="n">
         <v>6.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.93</v>
@@ -2168,16 +2168,16 @@
         <v>5.07</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD13" t="n">
         <v>6</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,70 +2258,70 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="N14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O14" t="n">
         <v>2.05</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.95</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="T14" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AE14" t="n">
         <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AH14" t="n">
         <v>11</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.85</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S15" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="V15" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>4.33</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>2.07</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>15</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.12</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.03</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="M3" t="n">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
         <v>1.8</v>
@@ -860,10 +860,10 @@
         <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.53</v>
@@ -983,7 +983,7 @@
         <v>1.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AB4" t="n">
         <v>1.55</v>
@@ -992,16 +992,16 @@
         <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
         <v>4</v>
@@ -1070,28 +1070,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="Q5" t="n">
         <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
         <v>2.25</v>
@@ -1103,13 +1103,13 @@
         <v>4.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
         <v>1.16</v>
@@ -1118,10 +1118,10 @@
         <v>4.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
         <v>2.3</v>
@@ -1133,7 +1133,7 @@
         <v>1.47</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH5" t="n">
         <v>3.8</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>4.15</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
         <v>10</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>1.17</v>
       </c>
-      <c r="Y11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.04</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.33</v>
+        <v>2.37</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.95</v>
+        <v>2.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
         <v>4.2</v>
       </c>
       <c r="U12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.17</v>
       </c>
-      <c r="V12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y12" t="n">
-        <v>5.17</v>
+        <v>4.71</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD12" t="n">
         <v>6.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AH12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,46 +2126,46 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.93</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="U13" t="n">
         <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
         <v>1.5</v>
@@ -2174,28 +2174,28 @@
         <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AE13" t="n">
         <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
         <v>11</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,70 +2258,70 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="P14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Z14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.45</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB14" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AH14" t="n">
         <v>11</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.25</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="T15" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>9.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="Z15" t="n">
         <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
         <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>15.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>5.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>3.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.37</v>
+        <v>1.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.28</v>
+        <v>6.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>19.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R4" t="n">
         <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V4" t="n">
         <v>4.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.55</v>
       </c>
-      <c r="AC4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>19.25</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
         <v>4.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD5" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.44</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH11" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>3.77</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.18</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,43 +2126,43 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="T13" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
         <v>5</v>
@@ -2171,25 +2171,25 @@
         <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
         <v>11</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,46 +2258,46 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.25</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.3</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="Z14" t="n">
         <v>1.5</v>
@@ -2306,28 +2306,28 @@
         <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.99</v>
+        <v>3.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="P16" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
         <v>4.2</v>
       </c>
       <c r="U16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V16" t="n">
+        <v>9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.17</v>
       </c>
-      <c r="V16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y16" t="n">
-        <v>5.17</v>
+        <v>4.71</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD16" t="n">
         <v>6.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AH16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
         <v>2.5</v>
@@ -2822,16 +2822,16 @@
         <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB18" t="n">
         <v>1.64</v>
@@ -2840,10 +2840,10 @@
         <v>2.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
         <v>1.62</v>
@@ -2852,10 +2852,10 @@
         <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="O2" t="n">
         <v>1.8</v>
@@ -692,22 +692,22 @@
         <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
         <v>4.55</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -722,10 +722,10 @@
         <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
         <v>2.2</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
         <v>1.67</v>
@@ -1223,55 +1223,55 @@
         <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
         <v>2.04</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1334,34 +1334,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.4</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.46</v>
-      </c>
       <c r="T7" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
         <v>8.4</v>
@@ -1370,40 +1370,40 @@
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="Z7" t="n">
         <v>1.37</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.77</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>4.15</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.17</v>
       </c>
-      <c r="Y11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>4.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.04</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.95</v>
+        <v>2.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.62</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>4.15</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>6.75</v>
+        <v>10</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.23</v>
+        <v>5.95</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>2.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="S15" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.07</v>
+        <v>4.71</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AE15" t="n">
         <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="T16" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.71</v>
+        <v>5.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
         <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -670,17 +670,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="M2" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
         <v>1.8</v>
@@ -698,56 +698,56 @@
         <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="V2" t="n">
-        <v>4.55</v>
+        <v>5.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>10.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AE2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.59</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG2" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.85</v>
+        <v>4.95</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.8</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" t="n">
         <v>2.05</v>
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.14</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="P4" t="n">
-        <v>19.25</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
         <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.16</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
         <v>2.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AE4" t="n">
         <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>19.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
         <v>1.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.55</v>
       </c>
-      <c r="AC5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1220,34 +1220,34 @@
         <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
         <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB6" t="n">
         <v>2.3</v>
@@ -1256,19 +1256,19 @@
         <v>1.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI6" t="n">
         <v>1</v>
@@ -1352,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T7" t="n">
         <v>3.1</v>
@@ -1364,43 +1364,43 @@
         <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
         <v>1.57</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
         <v>1.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AI7" t="n">
         <v>1.03</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
         <v>1.23</v>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45882.58333333334</v>
+        <v>45882.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.77</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>6.75</v>
+        <v>10.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>3.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>1.31</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.23</v>
+        <v>5.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="Z12" t="n">
         <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AE12" t="n">
         <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,34 +2126,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="S13" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
         <v>15</v>
@@ -2162,37 +2162,37 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Z13" t="n">
         <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
         <v>2.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI13" t="n">
         <v>1.03</v>
@@ -2276,28 +2276,28 @@
         <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.17</v>
+        <v>5.55</v>
       </c>
       <c r="Z14" t="n">
         <v>1.5</v>
@@ -2312,22 +2312,22 @@
         <v>1.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,70 +2390,70 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U15" t="n">
         <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.71</v>
+        <v>5.4</v>
       </c>
       <c r="Z15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.52</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.49</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>5.25</v>
+        <v>15.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="T16" t="n">
-        <v>4.05</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>9.9</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.02</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Y16" t="n">
-        <v>5.07</v>
+        <v>10</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.4</v>
+        <v>3.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.89</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>2.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>5.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.53</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.25</v>
+        <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.53</v>
       </c>
-      <c r="P18" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.29</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>6.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.39</v>
+        <v>3.21</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1352,19 +1352,19 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
         <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1373,34 +1373,34 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AI7" t="n">
         <v>1.03</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>3.79</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>1.86</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.9</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.3</v>
-      </c>
       <c r="T14" t="n">
-        <v>4.1</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="V14" t="n">
-        <v>8.9</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.55</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.45</v>
+        <v>3.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.09</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.6</v>
+        <v>2.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="n">
-        <v>10</v>
+        <v>5.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
         <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
         <v>5.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="Z15" t="n">
         <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="P16" t="n">
-        <v>15.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="T16" t="n">
-        <v>2.49</v>
+        <v>4.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>9.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>2.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.23</v>
+        <v>6.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.22</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.53</v>
       </c>
-      <c r="P17" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.29</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>6.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>6.25</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.53</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V18" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.25</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -789,20 +789,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -879,12 +879,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AL3" s="3" t="n">
@@ -921,20 +921,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63', '90']</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '57']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
@@ -1317,20 +1317,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '34', '73']</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,76 +1466,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.79</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.86</v>
+        <v>1.23</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,73 +1862,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>5.3</v>
-      </c>
       <c r="Z11" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI11" t="n">
         <v>1.03</v>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,76 +1994,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.25</v>
       </c>
-      <c r="N12" t="n">
-        <v>5.3</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S12" t="n">
         <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,73 +2126,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>1.93</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="T13" t="n">
         <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AC13" t="n">
         <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.5</v>
+        <v>6.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AI13" t="n">
         <v>1.03</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,76 +2258,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.77</v>
+        <v>2.65</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.11</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.22</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,76 +2390,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.35</v>
+        <v>1.49</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>15.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>4.1</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>8.9</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.55</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.09</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.6</v>
+        <v>2.55</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>4.48</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,76 +2522,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="S16" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.1</v>
+        <v>5.15</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.53</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.25</v>
+        <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.53</v>
       </c>
-      <c r="P18" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.29</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="V18" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>6.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -1452,17 +1452,17 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1836,16 +1836,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1858,35 +1858,35 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
         <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
         <v>1.18</v>
@@ -1895,47 +1895,47 @@
         <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
         <v>2.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
         <v>1.53</v>
       </c>
       <c r="AH11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>1.03</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -1968,16 +1968,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1990,35 +1990,35 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M12" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
         <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U12" t="n">
         <v>1.18</v>
@@ -2027,47 +2027,47 @@
         <v>9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
         <v>2.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
         <v>1.53</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
         <v>1.03</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2100,111 +2100,111 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.62</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>1.93</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
         <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Y13" t="n">
         <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AC13" t="n">
         <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.17</v>
+        <v>6.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AI13" t="n">
         <v>1.03</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2232,16 +2232,16 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2254,84 +2254,84 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="M14" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.95</v>
+        <v>1.93</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="T14" t="n">
         <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
         <v>5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AA14" t="n">
         <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AC14" t="n">
         <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="AE14" t="n">
         <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AI14" t="n">
         <v>1.03</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,80 +1862,80 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2100,25 +2100,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2126,22 +2126,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
         <v>2.65</v>
       </c>
       <c r="N13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.05</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.95</v>
       </c>
       <c r="P13" t="n">
         <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
         <v>1.72</v>
@@ -2153,58 +2153,58 @@
         <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AC13" t="n">
         <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.25</v>
+        <v>5.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>1.03</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL13" s="3" t="n">
@@ -2496,25 +2496,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2522,85 +2522,85 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="T16" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.03</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AL16" s="3" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,76 +2654,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.53</v>
       </c>
-      <c r="P17" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.29</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>6.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,76 +2786,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>6.25</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.53</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V18" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.25</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,115 +513,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>Odd_A_HT</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>HT_Odd_Under05</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_H_HT1</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_D_HT1</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_A_HT1</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>awayGoals</t>
+          <t>Odd_DNB_H</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_DNB_A</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_H</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_A</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -686,76 +701,85 @@
         <v>1.8</v>
       </c>
       <c r="P2" t="n">
-        <v>17.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.1</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['84']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AO2" s="3" t="n">
         <v>45882.25</v>
       </c>
     </row>
@@ -818,76 +842,85 @@
         <v>1.8</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AO3" s="3" t="n">
         <v>45882.38541666666</v>
       </c>
     </row>
@@ -950,76 +983,85 @@
         <v>1.53</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>['63', '90']</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['13', '57']</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.5</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>['63', '90']</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>['13', '57']</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AO4" s="3" t="n">
         <v>45882.41666666666</v>
       </c>
     </row>
@@ -1082,76 +1124,85 @@
         <v>1.8</v>
       </c>
       <c r="P5" t="n">
-        <v>19.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN5" t="n">
         <v>2.05</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AO5" s="3" t="n">
         <v>45882.41666666666</v>
       </c>
     </row>
@@ -1214,76 +1265,85 @@
         <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>7.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN6" t="n">
         <v>2.75</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AO6" s="3" t="n">
         <v>45882.45833333334</v>
       </c>
     </row>
@@ -1349,73 +1409,82 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="S7" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="V7" t="n">
-        <v>8.300000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.4</v>
+        <v>1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.35</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.74</v>
+        <v>1.22</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.9</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>['17', '34', '73']</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>7.3</v>
+        <v>2.78</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>['17', '34', '73']</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="3" t="n">
         <v>45882.5</v>
       </c>
     </row>
@@ -1478,76 +1547,85 @@
         <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN8" t="n">
         <v>1.67</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>['45+2']</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AO8" s="3" t="n">
         <v>45882.54166666666</v>
       </c>
     </row>
@@ -1634,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1646,16 +1724,20 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1669,17 +1751,22 @@
       <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="3" t="n">
         <v>45882.54166666666</v>
       </c>
     </row>
@@ -1783,11 +1870,15 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1801,17 +1892,22 @@
       <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="3" t="n">
         <v>45882.54166666666</v>
       </c>
     </row>
@@ -1874,76 +1970,85 @@
         <v>1.67</v>
       </c>
       <c r="P11" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN11" t="n">
         <v>3.2</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+      <c r="AO11" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2006,76 +2111,85 @@
         <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>5.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN12" t="n">
         <v>2.1</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AO12" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2138,76 +2252,85 @@
         <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN13" t="n">
         <v>2.45</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V13" t="n">
-        <v>9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+      <c r="AO13" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2270,76 +2393,85 @@
         <v>1.93</v>
       </c>
       <c r="P14" t="n">
-        <v>5.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN14" t="n">
         <v>2.55</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V14" t="n">
-        <v>13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AO14" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2402,76 +2534,85 @@
         <v>1.59</v>
       </c>
       <c r="P15" t="n">
-        <v>15.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.36</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN15" t="n">
         <v>2.36</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+      <c r="AO15" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2534,76 +2675,85 @@
         <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.8</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V16" t="n">
-        <v>15</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+      <c r="AJ16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO16" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2666,76 +2816,85 @@
         <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>6.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN17" t="n">
         <v>2.1</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V17" t="n">
-        <v>11</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+      <c r="AO17" s="3" t="n">
         <v>45882.79166666666</v>
       </c>
     </row>
@@ -2798,76 +2957,85 @@
         <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.5</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
         <v>1.53</v>
       </c>
-      <c r="V18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AN18" t="n">
         <v>2.5</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+      <c r="AO18" s="3" t="n">
         <v>45882.79166666666</v>
       </c>
     </row>
@@ -2930,76 +3098,85 @@
         <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN19" t="n">
         <v>3.4</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>10</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
+      <c r="AO19" s="3" t="n">
         <v>45882.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -945,25 +945,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -971,83 +971,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
         <v>1.02</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="X4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Y4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI4" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>['63', '90']</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['13', '57']</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>45882.41666666666</v>
@@ -1086,109 +1086,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
         <v>1.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="X5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['63', '90']</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['13', '57']</t>
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>45882.41666666666</v>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,83 +1958,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="U11" t="n">
         <v>1.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="X11" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Y11" t="n">
         <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.15</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.13</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.49</v>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH11" t="n">
-        <v>2.59</v>
+        <v>3.26</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5.7</v>
+        <v>4.34</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45882.60416666666</v>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,62 +2099,62 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="U12" t="n">
         <v>1.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="X12" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y12" t="n">
         <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="AA12" t="n">
         <v>1.13</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.26</v>
+        <v>2.59</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.34</v>
+        <v>5.7</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45882.60416666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,62 +2240,62 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.55</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AA13" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.58</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.45</v>
+        <v>6</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45882.60416666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,62 +2522,62 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="N15" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.7</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.55</v>
+        <v>5.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.85</v>
+        <v>3.58</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>4.45</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45882.60416666666</v>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO19"/>
+  <dimension ref="A1:AK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,130 +513,110 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Odd_A_HT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>FT_Odd_Over05</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>homeGoals</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>awayGoals</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_HT1</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT1</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT1</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_H</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_A</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -698,88 +678,76 @@
         <v>2.75</v>
       </c>
       <c r="O2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.8</v>
       </c>
-      <c r="P2" t="n">
+      <c r="AJ2" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>['84']</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AK2" s="3" t="n">
         <v>45882.25</v>
       </c>
     </row>
@@ -839,88 +807,76 @@
         <v>2.3</v>
       </c>
       <c r="O3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.8</v>
       </c>
-      <c r="P3" t="n">
+      <c r="AJ3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO3" s="3" t="n">
+      <c r="AK3" s="3" t="n">
         <v>45882.38541666666</v>
       </c>
     </row>
@@ -945,123 +901,111 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.25</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AA4" t="n">
-        <v>1.41</v>
+        <v>2.48</v>
       </c>
       <c r="AB4" t="n">
         <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
+        <v>1.67</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.92</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.27</v>
+          <t>['63', '90']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['13', '57']</t>
+        </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.77</v>
+        <v>1.12</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO4" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45882.41666666666</v>
       </c>
     </row>
@@ -1086,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1112,97 +1056,85 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.26</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.02</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="W5" t="n">
-        <v>4.7</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.57</v>
+        <v>4.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="AA5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.55</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>['63', '90']</t>
-        </is>
+      <c r="AD5" t="n">
+        <v>2.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['13', '57']</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.12</v>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
       </c>
       <c r="AG5" t="n">
-        <v>2.9</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO5" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45882.41666666666</v>
       </c>
     </row>
@@ -1262,88 +1194,76 @@
         <v>3.35</v>
       </c>
       <c r="O6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.67</v>
       </c>
-      <c r="P6" t="n">
+      <c r="AJ6" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO6" s="3" t="n">
+      <c r="AK6" s="3" t="n">
         <v>45882.45833333334</v>
       </c>
     </row>
@@ -1403,88 +1323,76 @@
         <v>3.21</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.44</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>2.52</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>2.9</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>1.03</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>1.35</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>2.74</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>2.14</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>1.64</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>3.8</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>1.22</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>1.86</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>1.9</v>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>['17', '34', '73']</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>['90+3']</t>
         </is>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>1.32</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH7" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45882.5</v>
       </c>
     </row>
@@ -1544,88 +1452,76 @@
         <v>1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.39</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>2.7</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>2.94</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1.37</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>1.01</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>1.36</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>2.97</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>2.05</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>1.68</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>3.3</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>['45+2']</t>
         </is>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>1.3</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>1.13</v>
       </c>
-      <c r="AH8" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AI8" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AN8" t="n">
         <v>1.67</v>
       </c>
-      <c r="AO8" s="3" t="n">
+      <c r="AK8" s="3" t="n">
         <v>45882.54166666666</v>
       </c>
     </row>
@@ -1640,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,39 +1546,39 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1712,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1729,18 +1625,18 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD9" t="n">
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
+          <t>['39', '45+1', '54', '90']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1754,19 +1650,7 @@
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="3" t="n">
+      <c r="AK9" s="3" t="n">
         <v>45882.54166666666</v>
       </c>
     </row>
@@ -1776,31 +1660,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1813,102 +1697,90 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="inlineStr">
+        <v>2.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>45882.54166666666</v>
+        <v>2.1</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>45882.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1932,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,97 +1830,85 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>5.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.18</v>
+        <v>3.65</v>
       </c>
       <c r="U11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.08</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.62</v>
-      </c>
       <c r="W11" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Y11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z11" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AA11" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.13</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AC11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
+        <v>2.47</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.49</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.26</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO11" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK11" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2073,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,97 +1959,85 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>4.45</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.22</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.08</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.47</v>
-      </c>
       <c r="AC12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
+        <v>2.38</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.53</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF12" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.59</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AO12" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK12" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2204,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,97 +2088,85 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.49</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AI13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.55</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AO13" s="3" t="n">
+      <c r="AK13" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2345,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,97 +2217,85 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.62</v>
+        <v>1.49</v>
       </c>
       <c r="M14" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="P14" t="n">
         <v>2.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.63</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>2.19</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.18</v>
+        <v>2.36</v>
       </c>
       <c r="U14" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>2.15</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.17</v>
+        <v>2.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.11</v>
+        <v>2.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
+        <v>1.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.07</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AO14" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2496,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2522,97 +2346,85 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>2.65</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>5.77</v>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.72</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>2.15</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="Y15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>6.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
+        <v>2.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.29</v>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.58</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.76</v>
+        <v>2.95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AO15" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>45882.60416666666</v>
       </c>
     </row>
@@ -2622,31 +2434,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -2663,98 +2475,86 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.72</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['40', '57', '76', '89']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.15</v>
       </c>
-      <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>5.77</v>
-      </c>
       <c r="AI16" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO16" s="3" t="n">
-        <v>45882.60416666666</v>
+        <v>2.5</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45882.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2790,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2800,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2813,88 +2613,76 @@
         <v>2.7</v>
       </c>
       <c r="O17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['90+8']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2</v>
       </c>
-      <c r="P17" t="n">
+      <c r="AJ17" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO17" s="3" t="n">
+      <c r="AK17" s="3" t="n">
         <v>45882.79166666666</v>
       </c>
     </row>
@@ -2904,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,264 +2707,111 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="N18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.25</v>
       </c>
-      <c r="O18" t="n">
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.53</v>
       </c>
-      <c r="P18" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO18" s="3" t="n">
-        <v>45882.79166666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45882</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P19" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO19" s="3" t="n">
+      <c r="AK18" s="3" t="n">
         <v>45882.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-13.xlsx
+++ b/jogos_2025-08-13.xlsx
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC4" t="n">
         <v>1.55</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['63', '90']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['13', '57']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.9</v>
+        <v>1.77</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45882.41666666666</v>
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="n">
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['63', '90']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['13', '57']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45882.41666666666</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="M12" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.45</v>
+        <v>4.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="T12" t="n">
         <v>4</v>
@@ -1989,35 +1989,35 @@
         <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="Z12" t="n">
         <v>1.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.3</v>
+        <v>6.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45882.60416666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,65 +2088,65 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.62</v>
+        <v>1.49</v>
       </c>
       <c r="M13" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.28</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.83</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.17</v>
+        <v>2.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45882.60416666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,65 +2217,65 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.85</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.55</v>
+        <v>5.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45882.60416666666</v>
